--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -630,7 +630,6 @@
           <t>灯具</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>桌面</t>
@@ -713,7 +712,6 @@
           <t>桌椅</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>地面</t>
@@ -796,7 +794,6 @@
           <t>摆件</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>桌面</t>
@@ -879,7 +876,6 @@
           <t>桌椅</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>地面</t>
@@ -962,7 +958,6 @@
           <t>桌椅</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>地面</t>
@@ -1045,7 +1040,6 @@
           <t>桌椅</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>地面</t>
@@ -1128,7 +1122,6 @@
           <t>灯具</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>桌面</t>
@@ -1211,7 +1204,6 @@
           <t>盆栽</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>壁挂</t>
@@ -1224,12 +1216,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1294,7 +1286,6 @@
           <t>壁挂</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>壁挂</t>
@@ -1377,7 +1368,6 @@
           <t>灯具</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>桌面</t>
@@ -1460,7 +1450,6 @@
           <t>盆栽</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>地面</t>
@@ -1543,7 +1532,6 @@
           <t>摆件</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>桌面</t>
@@ -1626,7 +1614,6 @@
           <t>盆栽</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>地面</t>
@@ -1709,7 +1696,6 @@
           <t>摆件</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>地面</t>
@@ -1792,7 +1778,6 @@
           <t>壁挂</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>壁挂</t>

--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1844,6 +1844,180 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bed_side</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>单人床</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>躺下去就不想起来的床。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bed_front</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>床头床</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>床头是它的门面。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1844,6 +1844,990 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vanity</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>梳妆台</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>retro_radio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>复古收音机</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>桌面</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>music_player</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>音乐播放器</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>piano</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>钢琴</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>flashlight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>手电筒</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>桌面</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>熨斗</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>桌面</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>telescope</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>望远镜</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>桌面</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>colorful_cabinet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>彩色柜子</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>floor_lamp</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>落地灯</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>灯具</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>chalkboard</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>黑板</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>macaron_sofa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>马卡龙沙发</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>桌椅</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>metronome</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>节拍器</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>摆件</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>桌面</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="R7164366536a845e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="Ra9dd193a329b4a91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -535,20 +535,16 @@
           <x:t xml:space="preserve">table_lamp</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯</x:t>
-        </x:is>
+      <x:c r="B3" t="str">
+        <x:v>经典落地灯</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">灯具</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E3" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F3" t="inlineStr">
         <x:is>
@@ -556,20 +552,18 @@
         </x:is>
       </x:c>
       <x:c r="G3" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H3" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J3" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K3" t="inlineStr">
         <x:is>
@@ -603,20 +597,16 @@
           <x:t xml:space="preserve">round_table</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌</x:t>
-        </x:is>
+      <x:c r="B4" t="str">
+        <x:v>圆桌</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E4" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F4" t="inlineStr">
         <x:is>
@@ -624,7 +614,7 @@
         </x:is>
       </x:c>
       <x:c r="G4" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H4" s="2" t="n">
         <x:v>5</x:v>
@@ -634,10 +624,8 @@
           <x:t xml:space="preserve">30</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J4" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K4" t="inlineStr">
         <x:is>
@@ -650,19 +638,19 @@
         </x:is>
       </x:c>
       <x:c r="M4" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N4" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="O4" s="2" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="P4" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q4" s="2" t="n">
-        <x:v>135</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -671,20 +659,16 @@
           <x:t xml:space="preserve">crescent_aquarium</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月牙鱼缸</x:t>
-        </x:is>
+      <x:c r="B5" t="str">
+        <x:v>月牙鱼缸</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E5" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F5" t="inlineStr">
         <x:is>
@@ -692,7 +676,7 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="2" t="n">
         <x:v>1</x:v>
@@ -702,10 +686,8 @@
           <x:t xml:space="preserve">30</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J5" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K5" t="inlineStr">
         <x:is>
@@ -739,20 +721,16 @@
           <x:t xml:space="preserve">cat_sofa</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发</x:t>
-        </x:is>
+      <x:c r="B6" t="str">
+        <x:v>猫耳懒人沙发</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E6" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F6" t="inlineStr">
         <x:is>
@@ -760,7 +738,7 @@
         </x:is>
       </x:c>
       <x:c r="G6" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H6" s="2" t="n">
         <x:v>5</x:v>
@@ -770,10 +748,8 @@
           <x:t xml:space="preserve">25</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J6" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K6" t="inlineStr">
         <x:is>
@@ -807,20 +783,16 @@
           <x:t xml:space="preserve">single_sofa</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发</x:t>
-        </x:is>
+      <x:c r="B7" t="str">
+        <x:v>单人沙发</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E7" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F7" t="inlineStr">
         <x:is>
@@ -828,7 +800,7 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H7" s="2" t="n">
         <x:v>5</x:v>
@@ -838,10 +810,8 @@
           <x:t xml:space="preserve">32</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J7" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K7" t="inlineStr">
         <x:is>
@@ -875,20 +845,16 @@
           <x:t xml:space="preserve">armchair</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">扶手椅</x:t>
-        </x:is>
+      <x:c r="B8" t="str">
+        <x:v>扶手椅</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E8" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F8" t="inlineStr">
         <x:is>
@@ -896,7 +862,7 @@
         </x:is>
       </x:c>
       <x:c r="G8" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H8" s="2" t="n">
         <x:v>5</x:v>
@@ -906,10 +872,8 @@
           <x:t xml:space="preserve">30</x:t>
         </x:is>
       </x:c>
-      <x:c r="J8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J8" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K8" t="inlineStr">
         <x:is>
@@ -943,20 +907,16 @@
           <x:t xml:space="preserve">cactus_lamp</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯</x:t>
-        </x:is>
+      <x:c r="B9" t="str">
+        <x:v>仙人掌灯</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">灯具</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E9" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F9" t="inlineStr">
         <x:is>
@@ -974,10 +934,8 @@
           <x:t xml:space="preserve">15</x:t>
         </x:is>
       </x:c>
-      <x:c r="J9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J9" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K9" t="inlineStr">
         <x:is>
@@ -1011,20 +969,16 @@
           <x:t xml:space="preserve">hanging_plant</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植</x:t>
-        </x:is>
+      <x:c r="B10" t="str">
+        <x:v>悬挂绿植</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">盆栽</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
+      <x:c r="E10" t="str">
+        <x:v>壁挂</x:v>
       </x:c>
       <x:c r="F10" t="inlineStr">
         <x:is>
@@ -1032,7 +986,7 @@
         </x:is>
       </x:c>
       <x:c r="G10" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="2" t="n">
         <x:v>7</x:v>
@@ -1042,10 +996,8 @@
           <x:t xml:space="preserve">18</x:t>
         </x:is>
       </x:c>
-      <x:c r="J10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J10" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K10" t="inlineStr">
         <x:is>
@@ -1079,20 +1031,16 @@
           <x:t xml:space="preserve">landscape_poster</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报</x:t>
-        </x:is>
+      <x:c r="B11" t="str">
+        <x:v>风景海报</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">壁挂</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
+      <x:c r="E11" t="str">
+        <x:v>壁挂</x:v>
       </x:c>
       <x:c r="F11" t="inlineStr">
         <x:is>
@@ -1103,17 +1051,15 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H11" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">15</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J11" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K11" t="inlineStr">
         <x:is>
@@ -1147,20 +1093,16 @@
           <x:t xml:space="preserve">lava_lamp</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯</x:t>
-        </x:is>
+      <x:c r="B12" t="str">
+        <x:v>熔岩灯</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">灯具</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E12" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F12" t="inlineStr">
         <x:is>
@@ -1178,10 +1120,8 @@
           <x:t xml:space="preserve">15</x:t>
         </x:is>
       </x:c>
-      <x:c r="J12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J12" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K12" t="inlineStr">
         <x:is>
@@ -1215,20 +1155,16 @@
           <x:t xml:space="preserve">monstera</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹</x:t>
-        </x:is>
+      <x:c r="B13" t="str">
+        <x:v>龟背竹</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">盆栽</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E13" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F13" t="inlineStr">
         <x:is>
@@ -1236,7 +1172,7 @@
         </x:is>
       </x:c>
       <x:c r="G13" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H13" s="2" t="n">
         <x:v>5</x:v>
@@ -1246,10 +1182,8 @@
           <x:t xml:space="preserve">20</x:t>
         </x:is>
       </x:c>
-      <x:c r="J13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J13" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K13" t="inlineStr">
         <x:is>
@@ -1283,20 +1217,16 @@
           <x:t xml:space="preserve">orb_decoration</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件</x:t>
-        </x:is>
+      <x:c r="B14" t="str">
+        <x:v>球形摆件</x:v>
       </x:c>
       <x:c r="C14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E14" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F14" t="inlineStr">
         <x:is>
@@ -1304,7 +1234,7 @@
         </x:is>
       </x:c>
       <x:c r="G14" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="2" t="n">
         <x:v>1</x:v>
@@ -1314,10 +1244,8 @@
           <x:t xml:space="preserve">12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J14" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K14" t="inlineStr">
         <x:is>
@@ -1351,20 +1279,16 @@
           <x:t xml:space="preserve">potted_plant</x:t>
         </x:is>
       </x:c>
-      <x:c r="B15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物</x:t>
-        </x:is>
+      <x:c r="B15" t="str">
+        <x:v>盆栽植物</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">盆栽</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E15" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F15" t="inlineStr">
         <x:is>
@@ -1372,7 +1296,7 @@
         </x:is>
       </x:c>
       <x:c r="G15" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="2" t="n">
         <x:v>4</x:v>
@@ -1382,10 +1306,8 @@
           <x:t xml:space="preserve">12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J15" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K15" t="inlineStr">
         <x:is>
@@ -1419,20 +1341,16 @@
           <x:t xml:space="preserve">round_rug</x:t>
         </x:is>
       </x:c>
-      <x:c r="B16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯</x:t>
-        </x:is>
+      <x:c r="B16" t="str">
+        <x:v>圆形地毯</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E16" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F16" t="inlineStr">
         <x:is>
@@ -1440,7 +1358,7 @@
         </x:is>
       </x:c>
       <x:c r="G16" s="2" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="2" t="n">
         <x:v>8</x:v>
@@ -1450,10 +1368,8 @@
           <x:t xml:space="preserve">15</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J16" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K16" t="inlineStr">
         <x:is>
@@ -1487,20 +1403,16 @@
           <x:t xml:space="preserve">vintage_square_clock</x:t>
         </x:is>
       </x:c>
-      <x:c r="B17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟</x:t>
-        </x:is>
+      <x:c r="B17" t="str">
+        <x:v>复古方钟</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">壁挂</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
+      <x:c r="E17" t="str">
+        <x:v>壁挂</x:v>
       </x:c>
       <x:c r="F17" t="inlineStr">
         <x:is>
@@ -1508,7 +1420,7 @@
         </x:is>
       </x:c>
       <x:c r="G17" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="2" t="n">
         <x:v>5</x:v>
@@ -1518,10 +1430,8 @@
           <x:t xml:space="preserve">12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J17" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K17" t="inlineStr">
         <x:is>
@@ -1555,10 +1465,8 @@
           <x:t xml:space="preserve">bed_side</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床</x:t>
-        </x:is>
+      <x:c r="B18" t="str">
+        <x:v>单人床</x:v>
       </x:c>
       <x:c r="C18" t="inlineStr">
         <x:is>
@@ -1570,10 +1478,8 @@
           <x:t xml:space="preserve">躺下去就不想起来的床。</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E18" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F18" t="inlineStr">
         <x:is>
@@ -1591,10 +1497,8 @@
           <x:t xml:space="preserve">40</x:t>
         </x:is>
       </x:c>
-      <x:c r="J18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J18" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K18" t="inlineStr">
         <x:is>
@@ -1628,10 +1532,8 @@
           <x:t xml:space="preserve">bed_front</x:t>
         </x:is>
       </x:c>
-      <x:c r="B19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床</x:t>
-        </x:is>
+      <x:c r="B19" t="str">
+        <x:v>床头床</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr">
         <x:is>
@@ -1643,10 +1545,8 @@
           <x:t xml:space="preserve">床头是它的门面。</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E19" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F19" t="inlineStr">
         <x:is>
@@ -1664,10 +1564,8 @@
           <x:t xml:space="preserve">40</x:t>
         </x:is>
       </x:c>
-      <x:c r="J19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J19" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K19" t="inlineStr">
         <x:is>
@@ -1701,20 +1599,16 @@
           <x:t xml:space="preserve">vanity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">梳妆台</x:t>
-        </x:is>
+      <x:c r="B20" t="str">
+        <x:v>梳妆台</x:v>
       </x:c>
       <x:c r="C20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E20" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F20" t="inlineStr">
         <x:is>
@@ -1722,7 +1616,7 @@
         </x:is>
       </x:c>
       <x:c r="G20" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H20" s="2" t="n">
         <x:v>5</x:v>
@@ -1732,10 +1626,8 @@
           <x:t xml:space="preserve">35</x:t>
         </x:is>
       </x:c>
-      <x:c r="J20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J20" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K20" t="inlineStr">
         <x:is>
@@ -1769,20 +1661,16 @@
           <x:t xml:space="preserve">retro_radio</x:t>
         </x:is>
       </x:c>
-      <x:c r="B21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古收音机</x:t>
-        </x:is>
+      <x:c r="B21" t="str">
+        <x:v>复古收音机</x:v>
       </x:c>
       <x:c r="C21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E21" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F21" t="inlineStr">
         <x:is>
@@ -1800,10 +1688,8 @@
           <x:t xml:space="preserve">12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J21" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K21" t="inlineStr">
         <x:is>
@@ -1837,20 +1723,16 @@
           <x:t xml:space="preserve">music_player</x:t>
         </x:is>
       </x:c>
-      <x:c r="B22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">音乐播放器</x:t>
-        </x:is>
+      <x:c r="B22" t="str">
+        <x:v>音乐播放器</x:v>
       </x:c>
       <x:c r="C22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E22" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F22" t="inlineStr">
         <x:is>
@@ -1858,7 +1740,7 @@
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H22" s="2" t="n">
         <x:v>5</x:v>
@@ -1868,10 +1750,8 @@
           <x:t xml:space="preserve">20</x:t>
         </x:is>
       </x:c>
-      <x:c r="J22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J22" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K22" t="inlineStr">
         <x:is>
@@ -1905,20 +1785,16 @@
           <x:t xml:space="preserve">piano</x:t>
         </x:is>
       </x:c>
-      <x:c r="B23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">钢琴</x:t>
-        </x:is>
+      <x:c r="B23" t="str">
+        <x:v>钢琴</x:v>
       </x:c>
       <x:c r="C23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E23" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F23" t="inlineStr">
         <x:is>
@@ -1926,7 +1802,7 @@
         </x:is>
       </x:c>
       <x:c r="G23" s="2" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="2" t="n">
         <x:v>7</x:v>
@@ -1936,10 +1812,8 @@
           <x:t xml:space="preserve">40</x:t>
         </x:is>
       </x:c>
-      <x:c r="J23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J23" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K23" t="inlineStr">
         <x:is>
@@ -1973,20 +1847,16 @@
           <x:t xml:space="preserve">flashlight</x:t>
         </x:is>
       </x:c>
-      <x:c r="B24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手电筒</x:t>
-        </x:is>
+      <x:c r="B24" t="str">
+        <x:v>手电筒</x:v>
       </x:c>
       <x:c r="C24" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E24" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F24" t="inlineStr">
         <x:is>
@@ -2004,10 +1874,8 @@
           <x:t xml:space="preserve">8</x:t>
         </x:is>
       </x:c>
-      <x:c r="J24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J24" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K24" t="inlineStr">
         <x:is>
@@ -2041,20 +1909,16 @@
           <x:t xml:space="preserve">iron</x:t>
         </x:is>
       </x:c>
-      <x:c r="B25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熨斗</x:t>
-        </x:is>
+      <x:c r="B25" t="str">
+        <x:v>熨斗</x:v>
       </x:c>
       <x:c r="C25" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E25" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F25" t="inlineStr">
         <x:is>
@@ -2072,10 +1936,8 @@
           <x:t xml:space="preserve">8</x:t>
         </x:is>
       </x:c>
-      <x:c r="J25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J25" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K25" t="inlineStr">
         <x:is>
@@ -2109,20 +1971,16 @@
           <x:t xml:space="preserve">telescope</x:t>
         </x:is>
       </x:c>
-      <x:c r="B26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">望远镜</x:t>
-        </x:is>
+      <x:c r="B26" t="str">
+        <x:v>望远镜</x:v>
       </x:c>
       <x:c r="C26" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E26" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F26" t="inlineStr">
         <x:is>
@@ -2130,7 +1988,7 @@
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H26" s="2" t="n">
         <x:v>1</x:v>
@@ -2140,10 +1998,8 @@
           <x:t xml:space="preserve">10</x:t>
         </x:is>
       </x:c>
-      <x:c r="J26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J26" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K26" t="inlineStr">
         <x:is>
@@ -2177,20 +2033,16 @@
           <x:t xml:space="preserve">colorful_cabinet</x:t>
         </x:is>
       </x:c>
-      <x:c r="B27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">彩色柜子</x:t>
-        </x:is>
+      <x:c r="B27" t="str">
+        <x:v>彩色柜子</x:v>
       </x:c>
       <x:c r="C27" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E27" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F27" t="inlineStr">
         <x:is>
@@ -2198,7 +2050,7 @@
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H27" s="2" t="n">
         <x:v>5</x:v>
@@ -2208,10 +2060,8 @@
           <x:t xml:space="preserve">28</x:t>
         </x:is>
       </x:c>
-      <x:c r="J27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J27" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K27" t="inlineStr">
         <x:is>
@@ -2245,20 +2095,16 @@
           <x:t xml:space="preserve">floor_lamp</x:t>
         </x:is>
       </x:c>
-      <x:c r="B28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">落地灯</x:t>
-        </x:is>
+      <x:c r="B28" t="str">
+        <x:v>落地灯</x:v>
       </x:c>
       <x:c r="C28" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">灯具</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E28" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F28" t="inlineStr">
         <x:is>
@@ -2276,10 +2122,8 @@
           <x:t xml:space="preserve">18</x:t>
         </x:is>
       </x:c>
-      <x:c r="J28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J28" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K28" t="inlineStr">
         <x:is>
@@ -2313,20 +2157,16 @@
           <x:t xml:space="preserve">chalkboard</x:t>
         </x:is>
       </x:c>
-      <x:c r="B29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">黑板</x:t>
-        </x:is>
+      <x:c r="B29" t="str">
+        <x:v>黑板</x:v>
       </x:c>
       <x:c r="C29" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E29" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F29" t="inlineStr">
         <x:is>
@@ -2344,10 +2184,8 @@
           <x:t xml:space="preserve">15</x:t>
         </x:is>
       </x:c>
-      <x:c r="J29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J29" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K29" t="inlineStr">
         <x:is>
@@ -2381,20 +2219,16 @@
           <x:t xml:space="preserve">macaron_sofa</x:t>
         </x:is>
       </x:c>
-      <x:c r="B30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">马卡龙沙发</x:t>
-        </x:is>
+      <x:c r="B30" t="str">
+        <x:v>马卡龙沙发</x:v>
       </x:c>
       <x:c r="C30" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">桌椅</x:t>
         </x:is>
       </x:c>
-      <x:c r="E30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
+      <x:c r="E30" t="str">
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="F30" t="inlineStr">
         <x:is>
@@ -2402,7 +2236,7 @@
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H30" s="2" t="n">
         <x:v>5</x:v>
@@ -2412,10 +2246,8 @@
           <x:t xml:space="preserve">30</x:t>
         </x:is>
       </x:c>
-      <x:c r="J30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_1</x:t>
-        </x:is>
+      <x:c r="J30" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
       <x:c r="K30" t="inlineStr">
         <x:is>
@@ -2449,20 +2281,16 @@
           <x:t xml:space="preserve">metronome</x:t>
         </x:is>
       </x:c>
-      <x:c r="B31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">节拍器</x:t>
-        </x:is>
+      <x:c r="B31" t="str">
+        <x:v>节拍器</x:v>
       </x:c>
       <x:c r="C31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">摆件</x:t>
         </x:is>
       </x:c>
-      <x:c r="E31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌面</x:t>
-        </x:is>
+      <x:c r="E31" t="str">
+        <x:v>桌面</x:v>
       </x:c>
       <x:c r="F31" t="inlineStr">
         <x:is>
@@ -2480,10 +2308,8 @@
           <x:t xml:space="preserve">10</x:t>
         </x:is>
       </x:c>
-      <x:c r="J31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Pickup_260813_2</x:t>
-        </x:is>
+      <x:c r="J31" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
       <x:c r="K31" t="inlineStr">
         <x:is>

--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="Ra9dd193a329b4a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="R4696b7026553478d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -530,50 +530,39 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">table_lamp</x:t>
-        </x:is>
+      <x:c r="A3" t="str">
+        <x:v>table_lamp</x:v>
       </x:c>
       <x:c r="B3" t="str">
         <x:v>经典落地灯</x:v>
       </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灯具</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>灯具</x:v>
+      </x:c>
+      <x:c r="D3"/>
       <x:c r="E3" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F3" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G3" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H3" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J3" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K3" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M3" s="2" t="n">
         <x:v>3</x:v>
@@ -592,50 +581,39 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">round_table</x:t>
-        </x:is>
+      <x:c r="A4" t="str">
+        <x:v>round_table</x:v>
       </x:c>
       <x:c r="B4" t="str">
         <x:v>圆桌</x:v>
       </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D4"/>
       <x:c r="E4" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F4" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G4" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H4" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">30</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">是</x:t>
-        </x:is>
+      <x:c r="K4" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M4" s="2" t="n">
         <x:v>9</x:v>
@@ -654,26 +632,21 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">crescent_aquarium</x:t>
-        </x:is>
+      <x:c r="A5" t="str">
+        <x:v>crescent_aquarium</x:v>
       </x:c>
       <x:c r="B5" t="str">
         <x:v>月牙鱼缸</x:v>
       </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D5"/>
       <x:c r="E5" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F5" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G5" s="2" t="n">
         <x:v>4</x:v>
@@ -681,23 +654,17 @@
       <x:c r="H5" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">30</x:t>
-        </x:is>
+      <x:c r="I5" t="str">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J5" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K5" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M5" s="2" t="n">
         <x:v>3</x:v>
@@ -716,50 +683,39 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cat_sofa</x:t>
-        </x:is>
+      <x:c r="A6" t="str">
+        <x:v>cat_sofa</x:v>
       </x:c>
       <x:c r="B6" t="str">
         <x:v>猫耳懒人沙发</x:v>
       </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D6"/>
       <x:c r="E6" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F6" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G6" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H6" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">25</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J6" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K6" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M6" s="2" t="n">
         <x:v>3</x:v>
@@ -778,50 +734,39 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">single_sofa</x:t>
-        </x:is>
+      <x:c r="A7" t="str">
+        <x:v>single_sofa</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>单人沙发</x:v>
       </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D7"/>
       <x:c r="E7" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F7" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G7" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H7" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">32</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J7" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K7" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M7" s="2" t="n">
         <x:v>3</x:v>
@@ -840,50 +785,39 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">armchair</x:t>
-        </x:is>
+      <x:c r="A8" t="str">
+        <x:v>armchair</x:v>
       </x:c>
       <x:c r="B8" t="str">
         <x:v>扶手椅</x:v>
       </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D8"/>
       <x:c r="E8" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F8" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G8" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H8" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">30</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J8" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K8" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M8" s="2" t="n">
         <x:v>3</x:v>
@@ -902,26 +836,21 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cactus_lamp</x:t>
-        </x:is>
+      <x:c r="A9" t="str">
+        <x:v>cactus_lamp</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>仙人掌灯</x:v>
       </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灯具</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>灯具</x:v>
+      </x:c>
+      <x:c r="D9"/>
       <x:c r="E9" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F9" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G9" s="2" t="n">
         <x:v>3</x:v>
@@ -929,23 +858,17 @@
       <x:c r="H9" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
+      <x:c r="I9" t="str">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J9" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K9" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M9" s="2" t="n">
         <x:v>3</x:v>
@@ -964,50 +887,39 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">hanging_plant</x:t>
-        </x:is>
+      <x:c r="A10" t="str">
+        <x:v>hanging_plant</x:v>
       </x:c>
       <x:c r="B10" t="str">
         <x:v>悬挂绿植</x:v>
       </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>盆栽</x:v>
+      </x:c>
+      <x:c r="D10"/>
       <x:c r="E10" t="str">
         <x:v>壁挂</x:v>
       </x:c>
-      <x:c r="F10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F10" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G10" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">18</x:t>
-        </x:is>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J10" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K10" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L10" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M10" s="2" t="n">
         <x:v>3</x:v>
@@ -1026,50 +938,39 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">landscape_poster</x:t>
-        </x:is>
+      <x:c r="A11" t="str">
+        <x:v>landscape_poster</x:v>
       </x:c>
       <x:c r="B11" t="str">
         <x:v>风景海报</x:v>
       </x:c>
-      <x:c r="C11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D11"/>
       <x:c r="E11" t="str">
         <x:v>壁挂</x:v>
       </x:c>
-      <x:c r="F11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F11" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G11" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K11" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L11" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M11" s="2" t="n">
         <x:v>3</x:v>
@@ -1088,26 +989,21 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">lava_lamp</x:t>
-        </x:is>
+      <x:c r="A12" t="str">
+        <x:v>lava_lamp</x:v>
       </x:c>
       <x:c r="B12" t="str">
         <x:v>熔岩灯</x:v>
       </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灯具</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>灯具</x:v>
+      </x:c>
+      <x:c r="D12"/>
       <x:c r="E12" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F12" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G12" s="2" t="n">
         <x:v>2</x:v>
@@ -1115,23 +1011,17 @@
       <x:c r="H12" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
+      <x:c r="I12" t="str">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J12" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K12" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M12" s="2" t="n">
         <x:v>3</x:v>
@@ -1150,50 +1040,39 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">monstera</x:t>
-        </x:is>
+      <x:c r="A13" t="str">
+        <x:v>monstera</x:v>
       </x:c>
       <x:c r="B13" t="str">
         <x:v>龟背竹</x:v>
       </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>盆栽</x:v>
+      </x:c>
+      <x:c r="D13"/>
       <x:c r="E13" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F13" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G13" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H13" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K13" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M13" s="2" t="n">
         <x:v>3</x:v>
@@ -1212,26 +1091,21 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">orb_decoration</x:t>
-        </x:is>
+      <x:c r="A14" t="str">
+        <x:v>orb_decoration</x:v>
       </x:c>
       <x:c r="B14" t="str">
         <x:v>球形摆件</x:v>
       </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D14"/>
       <x:c r="E14" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F14" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G14" s="2" t="n">
         <x:v>3</x:v>
@@ -1239,23 +1113,17 @@
       <x:c r="H14" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12</x:t>
-        </x:is>
+      <x:c r="I14" t="str">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K14" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L14" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M14" s="2" t="n">
         <x:v>3</x:v>
@@ -1274,50 +1142,39 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">potted_plant</x:t>
-        </x:is>
+      <x:c r="A15" t="str">
+        <x:v>potted_plant</x:v>
       </x:c>
       <x:c r="B15" t="str">
         <x:v>盆栽植物</x:v>
       </x:c>
-      <x:c r="C15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>盆栽</x:v>
+      </x:c>
+      <x:c r="D15"/>
       <x:c r="E15" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F15" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G15" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K15" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M15" s="2" t="n">
         <x:v>3</x:v>
@@ -1336,50 +1193,39 @@
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">round_rug</x:t>
-        </x:is>
+      <x:c r="A16" t="str">
+        <x:v>round_rug</x:v>
       </x:c>
       <x:c r="B16" t="str">
         <x:v>圆形地毯</x:v>
       </x:c>
-      <x:c r="C16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D16"/>
       <x:c r="E16" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">是</x:t>
-        </x:is>
+      <x:c r="F16" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="G16" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K16" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M16" s="2" t="n">
         <x:v>3</x:v>
@@ -1398,50 +1244,39 @@
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vintage_square_clock</x:t>
-        </x:is>
+      <x:c r="A17" t="str">
+        <x:v>vintage_square_clock</x:v>
       </x:c>
       <x:c r="B17" t="str">
         <x:v>复古方钟</x:v>
       </x:c>
-      <x:c r="C17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D17"/>
       <x:c r="E17" t="str">
         <x:v>壁挂</x:v>
       </x:c>
-      <x:c r="F17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F17" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G17" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H17" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12</x:t>
-        </x:is>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K17" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M17" s="2" t="n">
         <x:v>3</x:v>
@@ -1460,55 +1295,41 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bed_side</x:t>
-        </x:is>
+      <x:c r="A18" t="str">
+        <x:v>bed_side</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>单人床</x:v>
       </x:c>
-      <x:c r="C18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">躺下去就不想起来的床。</x:t>
-        </x:is>
+      <x:c r="C18" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>躺下去就不想起来的床。</x:v>
       </x:c>
       <x:c r="E18" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F18" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G18" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">40</x:t>
-        </x:is>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J18" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K18" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M18" s="2" t="n">
         <x:v>3</x:v>
@@ -1527,55 +1348,41 @@
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bed_front</x:t>
-        </x:is>
+      <x:c r="A19" t="str">
+        <x:v>bed_front</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>床头床</x:v>
       </x:c>
-      <x:c r="C19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头是它的门面。</x:t>
-        </x:is>
+      <x:c r="C19" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>床头是它的门面。</x:v>
       </x:c>
       <x:c r="E19" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F19" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G19" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H19" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">40</x:t>
-        </x:is>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J19" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K19" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M19" s="2" t="n">
         <x:v>3</x:v>
@@ -1594,50 +1401,39 @@
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vanity</x:t>
-        </x:is>
+      <x:c r="A20" t="str">
+        <x:v>vanity</x:v>
       </x:c>
       <x:c r="B20" t="str">
         <x:v>梳妆台</x:v>
       </x:c>
-      <x:c r="C20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D20"/>
       <x:c r="E20" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F20" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G20" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H20" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">35</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K20" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L20" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M20" s="2" t="n">
         <x:v>3</x:v>
@@ -1656,26 +1452,21 @@
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">retro_radio</x:t>
-        </x:is>
+      <x:c r="A21" t="str">
+        <x:v>retro_radio</x:v>
       </x:c>
       <x:c r="B21" t="str">
         <x:v>复古收音机</x:v>
       </x:c>
-      <x:c r="C21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D21"/>
       <x:c r="E21" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F21" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G21" s="2" t="n">
         <x:v>4</x:v>
@@ -1683,23 +1474,17 @@
       <x:c r="H21" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12</x:t>
-        </x:is>
+      <x:c r="I21" t="str">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K21" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M21" s="2" t="n">
         <x:v>3</x:v>
@@ -1718,50 +1503,39 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">music_player</x:t>
-        </x:is>
+      <x:c r="A22" t="str">
+        <x:v>music_player</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>音乐播放器</x:v>
       </x:c>
-      <x:c r="C22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D22"/>
       <x:c r="E22" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F22" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G22" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H22" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K22" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L22" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M22" s="2" t="n">
         <x:v>3</x:v>
@@ -1780,50 +1554,39 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">piano</x:t>
-        </x:is>
+      <x:c r="A23" t="str">
+        <x:v>piano</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>钢琴</x:v>
       </x:c>
-      <x:c r="C23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D23"/>
       <x:c r="E23" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F23" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G23" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H23" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">40</x:t>
-        </x:is>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K23" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M23" s="2" t="n">
         <x:v>3</x:v>
@@ -1842,26 +1605,21 @@
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flashlight</x:t>
-        </x:is>
+      <x:c r="A24" t="str">
+        <x:v>flashlight</x:v>
       </x:c>
       <x:c r="B24" t="str">
         <x:v>手电筒</x:v>
       </x:c>
-      <x:c r="C24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D24"/>
       <x:c r="E24" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F24" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G24" s="2" t="n">
         <x:v>3</x:v>
@@ -1869,23 +1627,17 @@
       <x:c r="H24" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
+      <x:c r="I24" t="str">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K24" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M24" s="2" t="n">
         <x:v>3</x:v>
@@ -1904,26 +1656,21 @@
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">iron</x:t>
-        </x:is>
+      <x:c r="A25" t="str">
+        <x:v>iron</x:v>
       </x:c>
       <x:c r="B25" t="str">
         <x:v>熨斗</x:v>
       </x:c>
-      <x:c r="C25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D25"/>
       <x:c r="E25" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F25" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G25" s="2" t="n">
         <x:v>3</x:v>
@@ -1931,23 +1678,17 @@
       <x:c r="H25" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
+      <x:c r="I25" t="str">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K25" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M25" s="2" t="n">
         <x:v>3</x:v>
@@ -1966,26 +1707,21 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">telescope</x:t>
-        </x:is>
+      <x:c r="A26" t="str">
+        <x:v>telescope</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>望远镜</x:v>
       </x:c>
-      <x:c r="C26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D26"/>
       <x:c r="E26" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F26" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G26" s="2" t="n">
         <x:v>5</x:v>
@@ -1993,23 +1729,17 @@
       <x:c r="H26" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
+      <x:c r="I26" t="str">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K26" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M26" s="2" t="n">
         <x:v>3</x:v>
@@ -2028,50 +1758,39 @@
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">colorful_cabinet</x:t>
-        </x:is>
+      <x:c r="A27" t="str">
+        <x:v>colorful_cabinet</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>彩色柜子</x:v>
       </x:c>
-      <x:c r="C27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D27"/>
       <x:c r="E27" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F27" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G27" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="H27" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">28</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K27" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M27" s="2" t="n">
         <x:v>3</x:v>
@@ -2090,50 +1809,39 @@
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor_lamp</x:t>
-        </x:is>
+      <x:c r="A28" t="str">
+        <x:v>floor_lamp</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>落地灯</x:v>
       </x:c>
-      <x:c r="C28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灯具</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>灯具</x:v>
+      </x:c>
+      <x:c r="D28"/>
       <x:c r="E28" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F28" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G28" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H28" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">18</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K28" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M28" s="2" t="n">
         <x:v>3</x:v>
@@ -2152,50 +1860,39 @@
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">chalkboard</x:t>
-        </x:is>
+      <x:c r="A29" t="str">
+        <x:v>chalkboard</x:v>
       </x:c>
       <x:c r="B29" t="str">
         <x:v>黑板</x:v>
       </x:c>
-      <x:c r="C29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D29"/>
       <x:c r="E29" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F29" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G29" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="H29" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K29" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M29" s="2" t="n">
         <x:v>3</x:v>
@@ -2214,50 +1911,39 @@
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">macaron_sofa</x:t>
-        </x:is>
+      <x:c r="A30" t="str">
+        <x:v>macaron_sofa</x:v>
       </x:c>
       <x:c r="B30" t="str">
         <x:v>马卡龙沙发</x:v>
       </x:c>
-      <x:c r="C30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">桌椅</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D30"/>
       <x:c r="E30" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="F30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F30" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G30" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="H30" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">30</x:t>
-        </x:is>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>SoundEffect/2_Pickup_260813_1</x:v>
       </x:c>
-      <x:c r="K30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K30" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M30" s="2" t="n">
         <x:v>3</x:v>
@@ -2276,26 +1962,21 @@
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">metronome</x:t>
-        </x:is>
+      <x:c r="A31" t="str">
+        <x:v>metronome</x:v>
       </x:c>
       <x:c r="B31" t="str">
         <x:v>节拍器</x:v>
       </x:c>
-      <x:c r="C31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">摆件</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>摆件</x:v>
+      </x:c>
+      <x:c r="D31"/>
       <x:c r="E31" t="str">
         <x:v>桌面</x:v>
       </x:c>
-      <x:c r="F31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F31" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="G31" s="2" t="n">
         <x:v>3</x:v>
@@ -2303,23 +1984,17 @@
       <x:c r="H31" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10</x:t>
-        </x:is>
+      <x:c r="I31" t="str">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>SoundEffect/2_Pickup_260813_2</x:v>
       </x:c>
-      <x:c r="K31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SoundEffect/2_Putdown_260813</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="K31" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M31" s="2" t="n">
         <x:v>3</x:v>
@@ -2334,6 +2009,59 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q31" s="2" t="n">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>立柜</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>桌椅</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>兼具收纳与陈列功能的立式柜。</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="G32" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H32" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>SoundEffect/2_Pickup_260813_1</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>SoundEffect/2_Putdown_260813</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N32" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="P32" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Q32" t="n">
         <x:v>146</x:v>
       </x:c>
     </x:row>

--- a/Excel/家具族表.xlsx
+++ b/Excel/家具族表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="R4696b7026553478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具族" sheetId="1" r:id="Rbda422943959431f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -547,10 +547,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G3" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H3" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I3" t="str">
         <x:v>12</x:v>
@@ -598,10 +598,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G4" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H4" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I4" t="str">
         <x:v>30</x:v>
@@ -649,7 +649,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G5" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="2" t="n">
         <x:v>1</x:v>
@@ -700,10 +700,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G6" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I6" t="str">
         <x:v>25</x:v>
@@ -751,10 +751,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G7" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H7" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I7" t="str">
         <x:v>32</x:v>
@@ -802,10 +802,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G8" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H8" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" t="str">
         <x:v>30</x:v>
@@ -853,7 +853,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G9" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H9" s="2" t="n">
         <x:v>1</x:v>
@@ -1057,10 +1057,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G13" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H13" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I13" t="str">
         <x:v>20</x:v>
@@ -1159,10 +1159,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G15" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I15" t="str">
         <x:v>12</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I16" t="str">
         <x:v>15</x:v>
@@ -1317,7 +1317,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I18" t="str">
         <x:v>40</x:v>
@@ -1370,7 +1370,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H19" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I19" t="str">
         <x:v>40</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H20" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I20" t="str">
         <x:v>35</x:v>
@@ -1520,10 +1520,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G22" s="2" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I22" t="str">
         <x:v>20</x:v>
@@ -1571,10 +1571,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G23" s="2" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H23" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I23" t="str">
         <x:v>40</x:v>
@@ -1673,7 +1673,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G25" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H25" s="2" t="n">
         <x:v>1</x:v>
@@ -1724,7 +1724,7 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G26" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H26" s="2" t="n">
         <x:v>1</x:v>
@@ -1778,7 +1778,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H27" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I27" t="str">
         <x:v>28</x:v>
@@ -1826,10 +1826,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G28" s="2" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H28" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I28" t="str">
         <x:v>18</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H29" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I29" t="str">
         <x:v>15</x:v>
@@ -1928,10 +1928,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G30" s="2" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H30" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I30" t="str">
         <x:v>30</x:v>
@@ -2032,10 +2032,10 @@
         <x:v>否</x:v>
       </x:c>
       <x:c r="G32" s="2" t="n">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H32" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I32" t="n">
         <x:v>28</x:v>
